--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487817_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487817_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2926</v>
+        <v>7.0381</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5624</v>
+        <v>5.0144</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7302</v>
+        <v>2.0238</v>
       </c>
       <c r="G2" t="n">
         <v>6.5261</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9101</v>
+        <v>1.6557</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.3834</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9786</v>
+        <v>1.2722</v>
       </c>
       <c r="V2" t="n">
         <v>0.9376</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0983</v>
+        <v>5.5332</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6662</v>
+        <v>3.1304</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4321</v>
+        <v>2.4027</v>
       </c>
       <c r="G3" t="n">
         <v>3.0085</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0492</v>
+        <v>1.4841</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1025</v>
+        <v>0.5668</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9467</v>
+        <v>0.9173</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2766</v>
+        <v>4.7729</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5855</v>
+        <v>3.401</v>
       </c>
       <c r="F4" t="n">
-        <v>2.691</v>
+        <v>1.3719</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3517</v>
+        <v>4.6284</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4455</v>
+        <v>6.6588</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9062</v>
+        <v>-2.0304</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8129999999999999</v>
+        <v>5.0695</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3055</v>
+        <v>6.3897</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1185</v>
+        <v>-1.3202</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5387</v>
+        <v>-0.4411</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7509</v>
+        <v>0.2692</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2123</v>
+        <v>-0.7103</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0061</v>
+        <v>0.977</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5219</v>
+        <v>0.0557</v>
       </c>
       <c r="U4" t="n">
-        <v>1.528</v>
+        <v>0.9212</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3351</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7099</v>
+        <v>4.3594</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2275</v>
+        <v>2.0794</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4824</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3624</v>
+        <v>1.3517</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8808</v>
+        <v>0.4455</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5184</v>
+        <v>0.9062</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2646</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3218</v>
+        <v>-0.3055</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0572</v>
+        <v>1.1185</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0978</v>
+        <v>0.5387</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5591</v>
+        <v>0.7509</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4613</v>
+        <v>-0.2123</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6388</v>
+        <v>1.0889</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7111</v>
+        <v>-0.0281</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9278</v>
+        <v>1.117</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7076</v>
+        <v>2.3351</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7076</v>
+        <v>2.3351</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6406</v>
+        <v>3.6094</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5623</v>
+        <v>2.1257</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0783</v>
+        <v>1.4838</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6284</v>
+        <v>2.8222</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6588</v>
+        <v>2.9446</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0304</v>
+        <v>-0.1225</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0695</v>
+        <v>2.9163</v>
       </c>
       <c r="K6" t="n">
-        <v>6.3897</v>
+        <v>2.7203</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3202</v>
+        <v>0.1959</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4411</v>
+        <v>-0.0941</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2692</v>
+        <v>0.2243</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7103</v>
+        <v>-0.3184</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1553</v>
+        <v>1.1005</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7829</v>
+        <v>0.02</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6277</v>
+        <v>1.0804</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9376</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4915</v>
+        <v>3.2561</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0371</v>
+        <v>0.715</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4544</v>
+        <v>2.5411</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8222</v>
+        <v>2.3624</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9446</v>
+        <v>2.8808</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1225</v>
+        <v>-0.5184</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9163</v>
+        <v>2.2646</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7203</v>
+        <v>2.3218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1959</v>
+        <v>-0.0572</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0941</v>
+        <v>0.0978</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2243</v>
+        <v>0.5591</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3184</v>
+        <v>-0.4613</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9825</v>
+        <v>1.1851</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.1986</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0511</v>
+        <v>0.9865</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9376</v>
+        <v>-0.7076</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9848</v>
+        <v>0.8972</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7353</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7201</v>
+        <v>1.5439</v>
       </c>
       <c r="G9" t="n">
         <v>-0.308</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1065</v>
+        <v>1.0189</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0033</v>
+        <v>0.0853</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1098</v>
+        <v>0.9336</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.799</v>
+        <v>-1.0339</v>
       </c>
       <c r="E10" t="n">
         <v>-1.2488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4498</v>
+        <v>0.2149</v>
       </c>
       <c r="G10" t="n">
         <v>0.1584</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4588</v>
+        <v>1.2239</v>
       </c>
       <c r="T10" t="n">
         <v>0.4534</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0054</v>
+        <v>0.7705</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6562</v>
+        <v>-6.4148</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2501</v>
+        <v>-5.1848</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4061</v>
+        <v>-1.23</v>
       </c>
       <c r="G11" t="n">
         <v>-0.18</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8318</v>
+        <v>1.0732</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3882</v>
+        <v>0.4534</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4437</v>
+        <v>0.6198</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1051</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>24.2607</v>
+        <v>25.2392</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4202</v>
+        <v>12.399</v>
       </c>
       <c r="F12" t="n">
-        <v>12.8403</v>
+        <v>12.8402</v>
       </c>
       <c r="G12" t="n">
         <v>22.9422</v>
@@ -1390,19 +1390,19 @@
         <v>12.4871</v>
       </c>
       <c r="S12" t="n">
-        <v>9.893699999999999</v>
+        <v>10.8725</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2101</v>
+        <v>2.1885</v>
       </c>
       <c r="U12" t="n">
-        <v>8.683999999999999</v>
+        <v>8.6837</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2913</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4663</v>
+        <v>5.466300000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-6.7575</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2535</v>
+        <v>2.3416</v>
       </c>
       <c r="E13" t="n">
         <v>1.2741</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9794</v>
+        <v>1.0675</v>
       </c>
       <c r="G13" t="n">
         <v>1.139</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2799</v>
+        <v>-0.1918</v>
       </c>
       <c r="T13" t="n">
         <v>-0.261</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0189</v>
+        <v>0.0692</v>
       </c>
       <c r="V13" t="n">
         <v>0.3538</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5477</v>
+        <v>-0.4825</v>
       </c>
       <c r="E14" t="n">
-        <v>0.748</v>
+        <v>0.2463</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2957</v>
+        <v>-0.7288</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9598</v>
+        <v>-2.4973</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.951</v>
+        <v>-0.6783</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9911</v>
+        <v>-1.819</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7549</v>
+        <v>1.0871</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4118</v>
+        <v>1.0569</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1667</v>
+        <v>0.0302</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7147</v>
+        <v>-3.5844</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5392</v>
+        <v>-1.7352</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1755</v>
+        <v>-1.8492</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2487</v>
+        <v>2.9137</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3797</v>
+        <v>-1.2557</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1338</v>
+        <v>-1.1977</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2459</v>
+        <v>-0.058</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5603</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1391</v>
+        <v>0.4266</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6994</v>
+        <v>-1.1196</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4973</v>
+        <v>-0.9598</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6783</v>
+        <v>-1.951</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.819</v>
+        <v>0.9911</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0871</v>
+        <v>0.7549</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0569</v>
+        <v>-0.4118</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0302</v>
+        <v>1.1667</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5844</v>
+        <v>-1.7147</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7352</v>
+        <v>-1.5392</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8492</v>
+        <v>-0.1755</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9137</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3335</v>
+        <v>-0.525</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3049</v>
+        <v>-0.4553</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0287</v>
+        <v>-0.0698</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0798</v>
+        <v>-0.9242</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8018999999999999</v>
+        <v>1.0162</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8817</v>
+        <v>-1.9404</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8819</v>
@@ -1702,13 +1702,13 @@
         <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.406</v>
+        <v>-1.2504</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1091</v>
+        <v>-0.8948</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2968</v>
+        <v>-0.3555</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7924</v>
+        <v>-2.2622</v>
       </c>
       <c r="E17" t="n">
         <v>-2.4857</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6932</v>
+        <v>0.2235</v>
       </c>
       <c r="G17" t="n">
         <v>-2.945</v>
@@ -1780,13 +1780,13 @@
         <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3875</v>
+        <v>-0.8572</v>
       </c>
       <c r="T17" t="n">
         <v>-1.0439</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6564</v>
+        <v>0.1866</v>
       </c>
       <c r="V17" t="n">
         <v>0.7076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6663</v>
+        <v>-2.5783</v>
       </c>
       <c r="E18" t="n">
         <v>-2.1599</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5065</v>
+        <v>-0.4184</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0232</v>
@@ -1858,13 +1858,13 @@
         <v>3.1218</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3081</v>
+        <v>-1.22</v>
       </c>
       <c r="T18" t="n">
         <v>-1.1091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.199</v>
+        <v>-0.1109</v>
       </c>
       <c r="V18" t="n">
         <v>0.5838</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9772</v>
+        <v>-3.036</v>
       </c>
       <c r="E19" t="n">
         <v>-1.6878</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2895</v>
+        <v>-1.3482</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8135</v>
@@ -1936,13 +1936,13 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9369</v>
+        <v>-0.9956</v>
       </c>
       <c r="T19" t="n">
         <v>-0.7829</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1539</v>
+        <v>-0.2127</v>
       </c>
       <c r="V19" t="n">
         <v>1.3975</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3205</v>
+        <v>-3.4951</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5522</v>
+        <v>-0.8737</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7683</v>
+        <v>-2.6215</v>
       </c>
       <c r="G20" t="n">
         <v>-2.766</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8032</v>
+        <v>-0.9778</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3295</v>
+        <v>-0.651</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4736</v>
+        <v>-0.3268</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5838</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0997</v>
+        <v>-3.9716</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4681</v>
+        <v>-0.5199</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6317</v>
+        <v>-3.4517</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9879</v>
+        <v>-2.0702</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8148</v>
+        <v>-2.5266</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1731</v>
+        <v>0.4564</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6692</v>
+        <v>0.1792</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7084</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>1.1667</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3187</v>
+        <v>-2.2495</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1064</v>
+        <v>-1.5392</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2123</v>
+        <v>-0.7103</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0406</v>
+        <v>1.0406</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6113</v>
+        <v>-0.9607</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7177</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1064</v>
+        <v>-0.2616</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4599</v>
+        <v>-1.9813</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4599</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3327</v>
+        <v>-4.1687</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7342</v>
+        <v>-3.3609</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5985</v>
+        <v>-0.8078</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0702</v>
+        <v>-1.9879</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5266</v>
+        <v>-1.8148</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4564</v>
+        <v>-0.1731</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1792</v>
+        <v>-0.6692</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-0.7084</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1667</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2495</v>
+        <v>-1.3187</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5392</v>
+        <v>-1.1064</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7103</v>
+        <v>-0.2123</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3218</v>
+        <v>-0.6803</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9134</v>
+        <v>-0.6105</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4084</v>
+        <v>-0.0698</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9813</v>
+        <v>-0.4599</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.9813</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1375</v>
+        <v>-4.9907</v>
       </c>
       <c r="E23" t="n">
         <v>-4.7157</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4219</v>
+        <v>-0.2751</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1363</v>
@@ -2248,13 +2248,13 @@
         <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1261</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-0.9786</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1474</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8751</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.2606</v>
+        <v>-24.2607</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.8405</v>
+        <v>-12.8404</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.4206</v>
+        <v>-11.4205</v>
       </c>
       <c r="G24" t="n">
         <v>-22.9421</v>
@@ -2302,10 +2302,10 @@
         <v>1.5733</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.5087</v>
+        <v>-2.508700000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>4.082100000000001</v>
+        <v>4.0821</v>
       </c>
       <c r="M24" t="n">
         <v>-24.5156</v>
@@ -2326,13 +2326,13 @@
         <v>19.7714</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.893999999999998</v>
+        <v>-9.893800000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-8.6839</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2098</v>
+        <v>-1.2099</v>
       </c>
       <c r="V24" t="n">
         <v>1.291399999999999</v>
